--- a/Outputs/Scenarios/PtX_demand_CZ_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_CZ_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.003083138472135582</v>
       </c>
       <c r="K16" t="n">
-        <v>1.331485135418556e-06</v>
+        <v>1.553399324654981e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>4.438283784728519e-07</v>
+        <v>4.660197973964945e-07</v>
       </c>
     </row>
     <row r="18">
@@ -1333,7 +1333,7 @@
         <v>0.0002470832921338098</v>
       </c>
       <c r="K24" t="n">
-        <v>1.220410924179229e-06</v>
+        <v>1.22041092417923e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1481,7 +1481,7 @@
         <v>4.442280650532449e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>4.438283784728519e-07</v>
+        <v>1.997227703127834e-07</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.004564211146989551</v>
       </c>
       <c r="K30" t="n">
-        <v>6.666335553477948e-06</v>
+        <v>7.777391479057606e-06</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2.222111851159316e-06</v>
+        <v>2.333217443717283e-06</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.0002402216393152396</v>
       </c>
       <c r="K42" t="n">
-        <v>2.222111851159316e-06</v>
+        <v>9.999503330216924e-07</v>
       </c>
     </row>
     <row r="43">
